--- a/data/trans_dic/IP13-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,62%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 9,81</t>
+          <t>3,18; 12,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 11,85</t>
+          <t>3,75; 14,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,13</t>
+          <t>0,98; 9,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 17,7</t>
+          <t>6,22; 21,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 13,07</t>
+          <t>2,23; 10,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 14,1</t>
+          <t>3,04; 12,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,68</t>
+          <t>0,9; 9,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 20,7</t>
+          <t>4,66; 18,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,69</t>
+          <t>3,7; 9,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,05</t>
+          <t>4,39; 10,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,0</t>
+          <t>1,57; 7,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 15,78</t>
+          <t>6,74; 17,4</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,32%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,84</t>
+          <t>3,16; 6,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,08</t>
+          <t>5,06; 8,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,8</t>
+          <t>3,55; 6,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,79</t>
+          <t>4,09; 7,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,18</t>
+          <t>3,45; 7,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,3</t>
+          <t>3,82; 7,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,72</t>
+          <t>3,63; 6,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,88</t>
+          <t>3,55; 6,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 5,95</t>
+          <t>3,63; 5,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,51</t>
+          <t>4,85; 7,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,22</t>
+          <t>3,93; 6,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,66</t>
+          <t>4,31; 6,78</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,1%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,07</t>
+          <t>2,92; 9,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,45</t>
+          <t>1,41; 6,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 10,23</t>
+          <t>1,9; 6,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,28</t>
+          <t>3,98; 11,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,93</t>
+          <t>1,3; 5,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,64</t>
+          <t>2,92; 8,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,53</t>
+          <t>4,01; 9,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,29</t>
+          <t>3,77; 11,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,18</t>
+          <t>2,63; 6,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,26</t>
+          <t>2,68; 6,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,07</t>
+          <t>3,35; 7,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,29</t>
+          <t>4,76; 9,72</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,77</t>
+          <t>3,84; 6,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,12</t>
+          <t>4,78; 7,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,7</t>
+          <t>3,27; 5,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,28</t>
+          <t>5,11; 8,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,31</t>
+          <t>3,22; 5,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,74</t>
+          <t>4,19; 7,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,79</t>
+          <t>4,03; 6,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,08</t>
+          <t>4,42; 7,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,68</t>
+          <t>3,92; 5,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,87</t>
+          <t>4,8; 6,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,77</t>
+          <t>4,04; 5,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,23</t>
+          <t>5,11; 7,42</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6052</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6931</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4726</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6072</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4901</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6052</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6931</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11505</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1966; 8913</t>
+          <t>2761; 10692</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2838; 10870</t>
+          <t>3233; 12760</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>529; 6018</t>
+          <t>671; 6615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2326; 9678</t>
+          <t>3530; 12339</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2798; 11347</t>
+          <t>2026; 9380</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3734; 12150</t>
+          <t>2790; 11022</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>666; 5954</t>
+          <t>536; 5532</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3670; 12838</t>
+          <t>2177; 8681</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6093; 17228</t>
+          <t>6569; 16991</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8372; 19665</t>
+          <t>7815; 19374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1710; 8963</t>
+          <t>2007; 9545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7002; 18408</t>
+          <t>6974; 18003</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21518</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33681</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23918</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27410</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20879</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24046</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23797</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22546</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21518</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23918</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>49286</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14668; 28480</t>
+          <t>15087; 29528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16179; 31954</t>
+          <t>24839; 43786</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17524; 32113</t>
+          <t>17334; 32911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14729; 31219</t>
+          <t>19465; 36701</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15532; 29474</t>
+          <t>14376; 29107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26414; 45703</t>
+          <t>17254; 33144</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16957; 32849</t>
+          <t>17161; 32291</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21305; 40706</t>
+          <t>15317; 29726</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33226; 53117</t>
+          <t>32399; 52396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46037; 70787</t>
+          <t>45771; 69984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38543; 59805</t>
+          <t>37766; 60338</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40922; 65039</t>
+          <t>39125; 61502</t>
         </is>
       </c>
     </row>
@@ -1784,37 +1784,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8559</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5488</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11321</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4805</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8503</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>11184</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9991</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8559</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5488</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6729</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21618</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2239; 8828</t>
+          <t>4625; 14380</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4536; 14098</t>
+          <t>2436; 10828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6921; 17674</t>
+          <t>3557; 12619</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6043; 16875</t>
+          <t>6685; 18551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4629; 14124</t>
+          <t>2268; 9005</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2322; 11433</t>
+          <t>4865; 14876</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3142; 12250</t>
+          <t>6926; 17041</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6891; 18786</t>
+          <t>5651; 16521</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8598; 20518</t>
+          <t>8752; 19998</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8604; 21221</t>
+          <t>9076; 21660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12016; 25478</t>
+          <t>12068; 26148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15078; 30851</t>
+          <t>15132; 30906</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36130</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>30410</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>38621</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>37065</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46100</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>82409</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22650; 39327</t>
+          <t>27703; 46220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29857; 50555</t>
+          <t>35863; 58838</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28561; 47171</t>
+          <t>24341; 43080</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27808; 48328</t>
+          <t>35761; 58317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27621; 45568</t>
+          <t>21917; 39561</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36085; 58002</t>
+          <t>29760; 50695</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24044; 43119</t>
+          <t>28392; 46841</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37418; 61482</t>
+          <t>27749; 47568</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54347; 79630</t>
+          <t>55062; 80101</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70412; 100300</t>
+          <t>70134; 100819</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57615; 83620</t>
+          <t>58617; 86489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71064; 103061</t>
+          <t>67829; 98519</t>
         </is>
       </c>
     </row>
